--- a/new-stats/abha-club.xlsx
+++ b/new-stats/abha-club.xlsx
@@ -511,22 +511,62 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>13/08/2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Abha</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Al Hazem</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N2" t="n">
+        <v>8</v>
+      </c>
+      <c r="O2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
